--- a/BeatnotePostHotCell/Jun11,2026/Fit_ResultJun11.xlsx
+++ b/BeatnotePostHotCell/Jun11,2026/Fit_ResultJun11.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostHotCell\Jun11,2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostHotCell\Jun11,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7519650C-4D50-45FD-A13C-74C0C0B844CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE8F560-506D-427F-B55A-8ED0206E5B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D9E101C5-8284-4B59-8B1C-2AD2D5F2FDD3}"/>
   </bookViews>
   <sheets>
     <sheet name="894" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="27">
   <si>
     <t>Date</t>
   </si>
@@ -120,31 +120,13 @@
   </si>
   <si>
     <t>Jun11,2026+5-37-55PM</t>
-  </si>
-  <si>
-    <t>Jun11,2026+10-52-10AM</t>
-  </si>
-  <si>
-    <t>Jun11,2026+12-39-36PM</t>
-  </si>
-  <si>
-    <t>Jun11,2026+3-55-37PM</t>
-  </si>
-  <si>
-    <t>Jun11,2026+4-14-43PM</t>
-  </si>
-  <si>
-    <t>Jun11,2026+9-56-07AM</t>
-  </si>
-  <si>
-    <t>Jun11,2026+4-50-26PM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -516,9 +498,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40C5617D-2BBC-4C21-ADC4-3687FEC8C6E3}">
   <dimension ref="A1:S33"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -551,7 +533,7 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -583,7 +565,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -608,7 +590,7 @@
       <c r="H3" s="1"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -633,7 +615,7 @@
       <c r="H4" s="1"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -658,7 +640,7 @@
       <c r="H5" s="1"/>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -683,7 +665,7 @@
       <c r="H6" s="1"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -708,7 +690,7 @@
       <c r="H7" s="1"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -733,7 +715,7 @@
       <c r="H8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -758,7 +740,7 @@
       <c r="H9" s="1"/>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -783,7 +765,7 @@
       <c r="H10" s="1"/>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -808,7 +790,7 @@
       <c r="H11" s="1"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -833,7 +815,7 @@
       <c r="H12" s="1"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -858,7 +840,7 @@
       <c r="H13" s="1"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
@@ -883,7 +865,7 @@
       <c r="H14" s="1"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
@@ -908,7 +890,7 @@
       <c r="H15" s="1"/>
       <c r="R15" s="1"/>
     </row>
-    <row r="16" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" ht="42.75">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -933,7 +915,7 @@
       <c r="H16" s="1"/>
       <c r="R16" s="1"/>
     </row>
-    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="42.75">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
@@ -957,7 +939,7 @@
       </c>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -967,7 +949,7 @@
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -977,7 +959,7 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -987,7 +969,7 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -997,7 +979,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1006,7 +988,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1015,7 +997,7 @@
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1024,7 +1006,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1033,7 +1015,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1042,7 +1024,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1051,7 +1033,7 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1060,7 +1042,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1069,7 +1051,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1078,7 +1060,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1087,7 +1069,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1096,7 +1078,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1113,9 +1095,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011646E0-737D-49FA-A2CA-7848F848076B}">
   <dimension ref="A1:T40"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1151,30 +1133,30 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="42.75">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1">
-        <v>8.9005463808524393E-2</v>
+        <v>6.9580113040116104E-2</v>
       </c>
       <c r="C2" s="1">
-        <v>1.55486488714376</v>
+        <v>1.55091524134111</v>
       </c>
       <c r="D2" s="1">
-        <v>1.5019662491822601E-3</v>
+        <v>1.3454091475730799E-3</v>
       </c>
       <c r="E2" s="1">
-        <v>-1.70304404390094E-4</v>
+        <v>-1.1962820817634099E-4</v>
       </c>
       <c r="F2" s="1">
-        <v>1.9777943119216299</v>
+        <v>1.6730295759310501</v>
       </c>
       <c r="G2" s="1">
-        <v>39.532378427738202</v>
+        <v>40.483422593478103</v>
       </c>
       <c r="H2" s="1">
-        <v>6.7267388421084998E-4</v>
+        <v>5.8007362629542705E-4</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1185,30 +1167,30 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="42.75">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1">
-        <v>8.8221156894290303E-2</v>
+        <v>7.0068196646880104E-2</v>
       </c>
       <c r="C3" s="1">
-        <v>1.5516997129364001</v>
+        <v>1.5512063773390801</v>
       </c>
       <c r="D3" s="1">
-        <v>1.8198170462488401E-3</v>
+        <v>1.33855994820921E-3</v>
       </c>
       <c r="E3" s="1">
-        <v>-2.6074580262228097E-4</v>
+        <v>-1.2867154682489601E-4</v>
       </c>
       <c r="F3" s="1">
-        <v>1.7216329871305001</v>
+        <v>1.9117333728349599</v>
       </c>
       <c r="G3" s="1">
-        <v>39.301288386472599</v>
+        <v>39.436185755626603</v>
       </c>
       <c r="H3" s="1">
-        <v>6.0549395822246505E-4</v>
+        <v>5.8220769436672498E-4</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1219,527 +1201,431 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="42.75">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1">
-        <v>8.9287039240001795E-2</v>
+        <v>7.0994631005327505E-2</v>
       </c>
       <c r="C4" s="1">
-        <v>1.55091524134111</v>
+        <v>1.5508671083397201</v>
       </c>
       <c r="D4" s="1">
-        <v>1.3454091475730799E-3</v>
+        <v>1.52933751865176E-3</v>
       </c>
       <c r="E4" s="1">
-        <v>-1.1962820817634099E-4</v>
+        <v>-1.57460416545163E-4</v>
       </c>
       <c r="F4" s="1">
-        <v>1.7342612208327099</v>
+        <v>1.6694511159867</v>
       </c>
       <c r="G4" s="1">
-        <v>39.680919273072497</v>
+        <v>39.314567591479999</v>
       </c>
       <c r="H4" s="1">
-        <v>6.5167813261114E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.6321296848941003E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="42.75">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1">
-        <v>8.9953273584561996E-2</v>
+        <v>7.01413654005653E-2</v>
       </c>
       <c r="C5" s="1">
-        <v>1.5512063773390801</v>
+        <v>1.55117767889363</v>
       </c>
       <c r="D5" s="1">
-        <v>1.33855994820921E-3</v>
-      </c>
-      <c r="E5" s="1">
-        <v>-1.2867154682489601E-4</v>
+        <v>1.1606296225717999E-3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>-8.5933812219673699E-5</v>
       </c>
       <c r="F5" s="1">
-        <v>1.97293394479315</v>
+        <v>1.66770081197015</v>
       </c>
       <c r="G5" s="1">
-        <v>39.347354807063603</v>
+        <v>39.543602096399098</v>
       </c>
       <c r="H5" s="1">
-        <v>6.0824183469856898E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.5438230696303703E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="42.75">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1">
-        <v>9.1230909809772498E-2</v>
+        <v>7.1625188956317504E-2</v>
       </c>
       <c r="C6" s="1">
-        <v>1.5508671083397201</v>
+        <v>1.54328875129271</v>
       </c>
       <c r="D6" s="1">
-        <v>1.52933751865176E-3</v>
+        <v>1.45083182877366E-3</v>
       </c>
       <c r="E6" s="1">
-        <v>-1.57460416545163E-4</v>
+        <v>-1.1680416437718E-4</v>
       </c>
       <c r="F6" s="1">
-        <v>1.7306480584623201</v>
+        <v>1.8783127298144999</v>
       </c>
       <c r="G6" s="1">
-        <v>39.409599382761101</v>
+        <v>40.862917980086998</v>
       </c>
       <c r="H6" s="1">
-        <v>1.1570180573611301E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.1220879363875101E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="42.75">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1">
-        <v>9.0037965159722497E-2</v>
+        <v>7.04951567436682E-2</v>
       </c>
       <c r="C7" s="1">
-        <v>1.55117767889363</v>
+        <v>1.54207790422821</v>
       </c>
       <c r="D7" s="1">
-        <v>1.1606296225717999E-3</v>
-      </c>
-      <c r="E7" s="2">
-        <v>-8.5933812219673699E-5</v>
+        <v>1.8871849890876201E-3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-1.6638071475920301E-4</v>
       </c>
       <c r="F7" s="1">
-        <v>1.7288929505491599</v>
+        <v>2.6714825283694998</v>
       </c>
       <c r="G7" s="1">
-        <v>39.502291420402301</v>
+        <v>39.815739114717502</v>
       </c>
       <c r="H7" s="1">
-        <v>6.0127654247993899E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.9356150306368596E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="42.75">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1">
-        <v>8.73991885500289E-2</v>
+        <v>7.1076737537177401E-2</v>
       </c>
       <c r="C8" s="1">
-        <v>1.5490580362570801</v>
+        <v>1.5407314258606899</v>
       </c>
       <c r="D8" s="1">
-        <v>1.9071072619291701E-3</v>
+        <v>2.0154893134944501E-3</v>
       </c>
       <c r="E8" s="1">
-        <v>-1.83025953123345E-4</v>
+        <v>-1.5456268555393601E-4</v>
       </c>
       <c r="F8" s="1">
-        <v>2.23238099678716</v>
+        <v>2.9029431890536999</v>
       </c>
       <c r="G8" s="1">
-        <v>39.332084701936203</v>
+        <v>41.383260946200103</v>
       </c>
       <c r="H8" s="1">
-        <v>5.9546486512800296E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.0456774869810001E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="42.75">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1">
-        <v>9.2063662732121604E-2</v>
+        <v>7.0296602179900303E-2</v>
       </c>
       <c r="C9" s="1">
-        <v>1.5436356571102301</v>
+        <v>1.5410500430673399</v>
       </c>
       <c r="D9" s="1">
-        <v>1.3651723277618699E-3</v>
+        <v>2.27786412698428E-3</v>
       </c>
       <c r="E9" s="1">
-        <v>-1.11031283867125E-4</v>
+        <v>-2.0779644854500501E-4</v>
       </c>
       <c r="F9" s="1">
-        <v>1.7293777380431601</v>
+        <v>2.9159705002635499</v>
       </c>
       <c r="G9" s="1">
-        <v>41.280387219501698</v>
+        <v>39.752896068265997</v>
       </c>
       <c r="H9" s="1">
-        <v>1.1137066582338801E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>8.4737484286365997E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="42.75">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B10" s="1">
-        <v>9.0566169869859395E-2</v>
+        <v>7.0157369715004997E-2</v>
       </c>
       <c r="C10" s="1">
-        <v>1.54207790422821</v>
+        <v>1.5350164983766901</v>
       </c>
       <c r="D10" s="1">
-        <v>1.8871849890876201E-3</v>
+        <v>1.87925369112614E-3</v>
       </c>
       <c r="E10" s="1">
-        <v>-1.6638071475920301E-4</v>
+        <v>-1.5891454320702899E-4</v>
       </c>
       <c r="F10" s="1">
-        <v>2.7326905162559898</v>
+        <v>2.6681859218239499</v>
       </c>
       <c r="G10" s="1">
-        <v>40.620173947877802</v>
+        <v>40.632752225054901</v>
       </c>
       <c r="H10" s="1">
-        <v>7.5220820553518997E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.5220842401617599E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="42.75">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B11" s="1">
-        <v>9.1281359996997199E-2</v>
+        <v>7.0955354830624304E-2</v>
       </c>
       <c r="C11" s="1">
-        <v>1.5407314258606899</v>
+        <v>1.53652411422879</v>
       </c>
       <c r="D11" s="1">
-        <v>2.0154893134944501E-3</v>
+        <v>1.49036080701047E-3</v>
       </c>
       <c r="E11" s="1">
-        <v>-1.5456268555393601E-4</v>
+        <v>-1.4474091243397901E-4</v>
       </c>
       <c r="F11" s="1">
-        <v>2.9641273031747999</v>
+        <v>1.6547510293194301</v>
       </c>
       <c r="G11" s="1">
-        <v>41.604483150780702</v>
+        <v>40.535754366001797</v>
       </c>
       <c r="H11" s="1">
-        <v>1.1519407269394101E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.1407199775801001E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="42.75">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1">
-        <v>8.9027477386042206E-2</v>
+        <v>7.0402355659330701E-2</v>
       </c>
       <c r="C12" s="1">
-        <v>1.5410924471191301</v>
+        <v>1.5345932960672799</v>
       </c>
       <c r="D12" s="1">
-        <v>2.1807125545882E-3</v>
+        <v>2.3468305655257099E-3</v>
       </c>
       <c r="E12" s="1">
-        <v>-2.0239158342417099E-4</v>
+        <v>-2.2769684078015399E-4</v>
       </c>
       <c r="F12" s="1">
-        <v>2.7237088303060202</v>
+        <v>2.9137065084310598</v>
       </c>
       <c r="G12" s="1">
-        <v>39.612797917157501</v>
+        <v>41.634252250556301</v>
       </c>
       <c r="H12" s="1">
-        <v>7.1898175808023405E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>1.1278070083280999E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="42.75">
       <c r="A13" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1">
-        <v>9.0246189977935598E-2</v>
+        <v>6.9408807064024997E-2</v>
       </c>
       <c r="C13" s="1">
-        <v>1.5410500430673399</v>
+        <v>1.5354346796843199</v>
       </c>
       <c r="D13" s="1">
-        <v>2.27786412698428E-3</v>
+        <v>2.0030429407681301E-3</v>
       </c>
       <c r="E13" s="1">
-        <v>-2.0779644854500501E-4</v>
+        <v>-2.0026870256848199E-4</v>
       </c>
       <c r="F13" s="1">
-        <v>2.97717031011502</v>
+        <v>2.6624965759713999</v>
       </c>
       <c r="G13" s="1">
-        <v>40.072668992647202</v>
+        <v>40.6491182711721</v>
       </c>
       <c r="H13" s="1">
-        <v>6.9524047856987597E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.5220853935363899E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="42.75">
       <c r="A14" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1">
-        <v>8.7987770056780296E-2</v>
+        <v>7.0420029676822898E-2</v>
       </c>
       <c r="C14" s="1">
-        <v>1.53638175746062</v>
+        <v>1.5340188127490999</v>
       </c>
       <c r="D14" s="1">
-        <v>1.63345205691684E-3</v>
+        <v>2.1581463655920298E-3</v>
       </c>
       <c r="E14" s="1">
-        <v>-1.3979739045362E-4</v>
+        <v>-1.9057196407786599E-4</v>
       </c>
       <c r="F14" s="1">
-        <v>1.98072981394425</v>
+        <v>2.9181285155443</v>
       </c>
       <c r="G14" s="1">
-        <v>39.630991487003598</v>
+        <v>39.641527263839002</v>
       </c>
       <c r="H14" s="1">
-        <v>6.79577641819961E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.7674197222551999E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="42.75">
       <c r="A15" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1">
-        <v>9.0180923883803096E-2</v>
+        <v>7.1119616242477604E-2</v>
       </c>
       <c r="C15" s="1">
-        <v>1.5350164983766901</v>
+        <v>1.53399556393425</v>
       </c>
       <c r="D15" s="1">
-        <v>1.87925369112614E-3</v>
+        <v>1.9604113931687298E-3</v>
       </c>
       <c r="E15" s="1">
-        <v>-1.5891454320702899E-4</v>
+        <v>-1.7763026472953299E-4</v>
       </c>
       <c r="F15" s="1">
-        <v>2.7293893032979701</v>
+        <v>2.91969648100482</v>
       </c>
       <c r="G15" s="1">
-        <v>41.632410445603703</v>
+        <v>41.365555746510303</v>
       </c>
       <c r="H15" s="1">
-        <v>1.02675812566378E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9.6540334642402205E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="42.75">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1">
-        <v>9.1038024594974204E-2</v>
+        <v>6.8778607126876098E-2</v>
       </c>
       <c r="C16" s="1">
-        <v>1.53652411422879</v>
+        <v>1.53621256575123</v>
       </c>
       <c r="D16" s="1">
-        <v>1.49036080701047E-3</v>
+        <v>1.5095276277618901E-3</v>
       </c>
       <c r="E16" s="1">
-        <v>-1.4474091243397901E-4</v>
+        <v>-1.5743523758064999E-4</v>
       </c>
       <c r="F16" s="1">
-        <v>1.7159224884469599</v>
+        <v>2.1603695020999498</v>
       </c>
       <c r="G16" s="1">
-        <v>40.639023324181103</v>
+        <v>39.666447593591101</v>
       </c>
       <c r="H16" s="1">
-        <v>7.5220872921886496E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.4567896381248003E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="42.75">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1">
-        <v>9.0356969610468907E-2</v>
+        <v>6.9985374084186203E-2</v>
       </c>
       <c r="C17" s="1">
-        <v>1.5345932960672799</v>
+        <v>1.53608925519313</v>
       </c>
       <c r="D17" s="1">
-        <v>2.3468305655257099E-3</v>
+        <v>1.3920505413377901E-3</v>
       </c>
       <c r="E17" s="1">
-        <v>-2.2769684078015399E-4</v>
+        <v>-1.2059805193785E-4</v>
       </c>
       <c r="F17" s="1">
-        <v>2.9749096957418102</v>
+        <v>2.1665289202312401</v>
       </c>
       <c r="G17" s="1">
-        <v>41.579137041028801</v>
+        <v>41.2559981996326</v>
       </c>
       <c r="H17" s="1">
-        <v>9.8378037108451302E-4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="1">
-        <v>8.8591528333953298E-2</v>
-      </c>
-      <c r="C18" s="1">
-        <v>1.5345652935815699</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2.2339460856781899E-3</v>
-      </c>
-      <c r="E18" s="1">
-        <v>-2.0685834308693701E-4</v>
-      </c>
-      <c r="F18" s="1">
-        <v>2.9796633550846301</v>
-      </c>
-      <c r="G18" s="1">
-        <v>39.662496178568603</v>
-      </c>
-      <c r="H18" s="1">
-        <v>7.7924522038304495E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="1">
-        <v>8.9055177802521202E-2</v>
-      </c>
-      <c r="C19" s="1">
-        <v>1.5354346796843199</v>
-      </c>
-      <c r="D19" s="1">
-        <v>2.0030429407681301E-3</v>
-      </c>
-      <c r="E19" s="1">
-        <v>-2.0026870256848199E-4</v>
-      </c>
-      <c r="F19" s="1">
-        <v>2.7236832575966798</v>
-      </c>
-      <c r="G19" s="1">
-        <v>39.684592649597398</v>
-      </c>
-      <c r="H19" s="1">
-        <v>8.1166481782320404E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="1">
-        <v>9.0556231765949805E-2</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1.5340188127490999</v>
-      </c>
-      <c r="D20" s="1">
-        <v>2.1581463655920298E-3</v>
-      </c>
-      <c r="E20" s="1">
-        <v>-1.9057196407786599E-4</v>
-      </c>
-      <c r="F20" s="1">
-        <v>2.97934314682503</v>
-      </c>
-      <c r="G20" s="1">
-        <v>41.017834932329599</v>
-      </c>
-      <c r="H20" s="1">
-        <v>1.1384933521348399E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="1">
-        <v>9.1259865204828206E-2</v>
-      </c>
-      <c r="C21" s="1">
-        <v>1.53399556393425</v>
-      </c>
-      <c r="D21" s="1">
-        <v>1.9604113931687298E-3</v>
-      </c>
-      <c r="E21" s="1">
-        <v>-1.7763026472953299E-4</v>
-      </c>
-      <c r="F21" s="1">
-        <v>2.9809152589710899</v>
-      </c>
-      <c r="G21" s="1">
-        <v>41.581631065126402</v>
-      </c>
-      <c r="H21" s="1">
-        <v>6.0472284454866302E-4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="1">
-        <v>8.8371089308141498E-2</v>
-      </c>
-      <c r="C22" s="1">
-        <v>1.53621256575123</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1.5095276277618901E-3</v>
-      </c>
-      <c r="E22" s="1">
-        <v>-1.5743523758064999E-4</v>
-      </c>
-      <c r="F22" s="1">
-        <v>2.22159514052144</v>
-      </c>
-      <c r="G22" s="1">
-        <v>39.846780598130302</v>
-      </c>
-      <c r="H22" s="1">
-        <v>1.02411675301716E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="1">
-        <v>8.9886315679026302E-2</v>
-      </c>
-      <c r="C23" s="1">
-        <v>1.53608925519313</v>
-      </c>
-      <c r="D23" s="1">
-        <v>1.3920505413377901E-3</v>
-      </c>
-      <c r="E23" s="1">
-        <v>-1.2059805193785E-4</v>
-      </c>
-      <c r="F23" s="1">
-        <v>2.2277206914751</v>
-      </c>
-      <c r="G23" s="1">
-        <v>41.475519473295201</v>
-      </c>
-      <c r="H23" s="1">
-        <v>8.4662924379177095E-4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+        <v>7.0055033895612096E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1749,7 +1635,7 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1759,7 +1645,7 @@
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1769,7 +1655,7 @@
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1779,7 +1665,7 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1789,7 +1675,7 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1799,7 +1685,7 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1809,7 +1695,7 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1819,7 +1705,7 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1829,7 +1715,7 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1839,7 +1725,7 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1849,7 +1735,7 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1859,7 +1745,7 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1869,7 +1755,7 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1879,7 +1765,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1889,7 +1775,7 @@
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1899,7 +1785,7 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1916,13 +1802,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF8CB368-1F4F-4C65-B86B-93EC676CB77B}">
-  <dimension ref="A1:H34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="6" max="6" width="16.7265625" customWidth="1"/>
+    <col min="6" max="6" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1933,7 +1819,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1941,7 +1827,7 @@
         <v>5.5657944042335004</v>
       </c>
       <c r="C2" s="1">
-        <v>8.9287039240001795E-2</v>
+        <v>6.9580113040116104E-2</v>
       </c>
       <c r="G2">
         <v>894</v>
@@ -1949,8 +1835,9 @@
       <c r="H2">
         <v>456</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="1:11" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1958,7 +1845,7 @@
         <v>5.4648667593817297</v>
       </c>
       <c r="C3" s="1">
-        <v>8.9953273584561996E-2</v>
+        <v>7.0068196646880104E-2</v>
       </c>
       <c r="F3" t="s">
         <v>1</v>
@@ -1969,10 +1856,11 @@
       </c>
       <c r="H3">
         <f>AVERAGE(C2:C33)</f>
-        <v>9.0198625899603951E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.0344094119331263E-2</v>
+      </c>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -1980,7 +1868,7 @@
         <v>5.6047427761818804</v>
       </c>
       <c r="C4" s="1">
-        <v>9.1230909809772498E-2</v>
+        <v>7.0994631005327505E-2</v>
       </c>
       <c r="F4" t="s">
         <v>2</v>
@@ -1991,10 +1879,11 @@
       </c>
       <c r="H4">
         <f>_xlfn.STDEV.S(C2:C33)</f>
-        <v>1.10716439187551E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.211297498026381E-4</v>
+      </c>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2002,7 +1891,7 @@
         <v>5.5960936640263199</v>
       </c>
       <c r="C5" s="1">
-        <v>9.0037965159722497E-2</v>
+        <v>7.01413654005653E-2</v>
       </c>
       <c r="F5" t="s">
         <v>3</v>
@@ -2013,10 +1902,11 @@
       </c>
       <c r="H5">
         <f>H4/H3/SQRT(COUNT(C2:C33))</f>
-        <v>3.0686841978830284E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>2.5628652939197649E-3</v>
+      </c>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -2024,10 +1914,11 @@
         <v>5.4713363021862502</v>
       </c>
       <c r="C6" s="1">
-        <v>9.2063662732121604E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.1625188956317504E-2</v>
+      </c>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -2035,10 +1926,11 @@
         <v>5.5409104673644096</v>
       </c>
       <c r="C7" s="1">
-        <v>9.0566169869859395E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.04951567436682E-2</v>
+      </c>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
@@ -2046,10 +1938,11 @@
         <v>5.55013048416959</v>
       </c>
       <c r="C8" s="1">
-        <v>9.1281359996997199E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.1076737537177401E-2</v>
+      </c>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -2057,10 +1950,11 @@
         <v>5.5616342974163304</v>
       </c>
       <c r="C9" s="1">
-        <v>9.0246189977935598E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.0296602179900303E-2</v>
+      </c>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -2068,10 +1962,11 @@
         <v>5.5301083552827803</v>
       </c>
       <c r="C10" s="1">
-        <v>8.7987770056780296E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.0157369715004997E-2</v>
+      </c>
+      <c r="K10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
@@ -2079,10 +1974,11 @@
         <v>5.4935494282478201</v>
       </c>
       <c r="C11" s="1">
-        <v>9.1038024594974204E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.0955354830624304E-2</v>
+      </c>
+      <c r="K11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>21</v>
       </c>
@@ -2090,10 +1986,11 @@
         <v>5.4627011461568502</v>
       </c>
       <c r="C12" s="1">
-        <v>9.0356969610468907E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.0402355659330701E-2</v>
+      </c>
+      <c r="K12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -2101,10 +1998,11 @@
         <v>5.5557750287565701</v>
       </c>
       <c r="C13" s="1">
-        <v>8.9055177802521202E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.9408807064024997E-2</v>
+      </c>
+      <c r="K13" s="1"/>
+    </row>
+    <row r="14" spans="1:11" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
@@ -2112,10 +2010,11 @@
         <v>5.5014512688728496</v>
       </c>
       <c r="C14" s="1">
-        <v>9.0556231765949805E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.0420029676822898E-2</v>
+      </c>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
@@ -2123,10 +2022,11 @@
         <v>5.4947589504036598</v>
       </c>
       <c r="C15" s="1">
-        <v>9.1259865204828206E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7.1119616242477604E-2</v>
+      </c>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" ht="42.75">
       <c r="A16" s="1" t="s">
         <v>25</v>
       </c>
@@ -2134,10 +2034,11 @@
         <v>5.5489303201094904</v>
       </c>
       <c r="C16" s="1">
-        <v>8.8371089308141498E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+        <v>6.8778607126876098E-2</v>
+      </c>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" ht="42.75">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
@@ -2145,90 +2046,91 @@
         <v>5.4160645106972503</v>
       </c>
       <c r="C17" s="1">
-        <v>8.9886315679026302E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+        <v>6.9985374084186203E-2</v>
+      </c>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3">
       <c r="C34" s="1"/>
     </row>
   </sheetData>
